--- a/www/download/IND.gross_output.s.mv.EXI382.xlsx
+++ b/www/download/IND.gross_output.s.mv.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>30702.625</t>
+          <t>44747315254.099</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19969.392</t>
+          <t>27834137396.5421</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>19352.518</t>
+          <t>26519583211.7165</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>20670.46</t>
+          <t>28904428973.6676</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>23624.359</t>
+          <t>33554136795.1571</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>23850.533</t>
+          <t>33834486436.2994</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>24923.269</t>
+          <t>35751345797.3948</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>28005.17</t>
+          <t>40794175258.5003</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>26705.554</t>
+          <t>38327064088.2249</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>31397.19</t>
+          <t>45558590197.2949</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>33234.104</t>
+          <t>48321819426.0623</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>31439.099</t>
+          <t>45242875312.684</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>29236.045</t>
+          <t>41463510778.5874</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>32658.893</t>
+          <t>47150768293.0445</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>33944.688</t>
+          <t>48905819532.3807</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>31305.501</t>
+          <t>44522628125.7205</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>35189.262</t>
+          <t>50575890649.5773</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>33493.155</t>
+          <t>47823470575.4806</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33460.248</t>
+          <t>47625646517.1512</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>27834.007</t>
+          <t>39907898422.3586</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>24293.441</t>
+          <t>34492180464.8117</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>23423.956</t>
+          <t>32783406322.0713</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>24220.136</t>
+          <t>33647634132.9447</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>25397.772</t>
+          <t>35344803447.0357</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>23288.566</t>
+          <t>32300380801.4458</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>24133.817</t>
+          <t>33818780716.5576</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>24565.549</t>
+          <t>34763908841.3031</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8762.459</t>
+          <t>10067302644.2584</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>8075.973</t>
+          <t>8990556206.09732</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>7939.189</t>
+          <t>8742849599.65601</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8306.067</t>
+          <t>9204051123.12158</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>8900.748</t>
+          <t>9949392766.04356</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8930.906</t>
+          <t>10027988367.55</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>9437.546</t>
+          <t>10761969455.0045</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>8855.672</t>
+          <t>9975375574.75127</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>8987.029</t>
+          <t>10091546016.502</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>9323.437</t>
+          <t>10560913858.196</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>9463.634</t>
+          <t>10762555576.3864</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>9447.793</t>
+          <t>10779779300.0264</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>9143.598</t>
+          <t>10379870501.2109</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>9891.437</t>
+          <t>11219669573.0171</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>9313.096</t>
+          <t>10449426885.9135</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>9596.454</t>
+          <t>10926637995.4288</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>10341.768</t>
+          <t>11914539840.4298</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>10679.946</t>
+          <t>12219069812.6929</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>10423.451</t>
+          <t>11936226128.6729</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>9125.13</t>
+          <t>10402760827.0911</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>8891.891</t>
+          <t>10091779852.4722</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>10114301326.7636</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>8834.985</t>
+          <t>9930809575.44356</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9704.933</t>
+          <t>11057067024.3782</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>10008.647</t>
+          <t>11361966926.928</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10451.357</t>
+          <t>11945878743.3438</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>10546.883</t>
+          <t>12048887635.2972</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>18371.013</t>
+          <t>22940755728.5398</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12127.386</t>
+          <t>14362143030.6067</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>13321.565</t>
+          <t>15534983165.3745</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>13636.563</t>
+          <t>15947811370.1489</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>13737.915</t>
+          <t>16232930918.8221</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>15241.983</t>
+          <t>17983768496.9914</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>16482.958</t>
+          <t>19622050520.6122</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>14869.372</t>
+          <t>17619250976.3742</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>13845.315</t>
+          <t>16227166326.3221</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>15407.266</t>
+          <t>18106427947.7261</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>15838.775</t>
+          <t>18722480707.9182</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>15740.381</t>
+          <t>18657258588.9242</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>14680.662</t>
+          <t>17207635107.9906</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>18012.813</t>
+          <t>21272187460.2408</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>15386.918</t>
+          <t>18261554061.053</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>16218.829</t>
+          <t>19202502000.5342</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>18514.948</t>
+          <t>22151426456.7908</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>17908.03</t>
+          <t>21383647968.6485</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>20560.832</t>
+          <t>24735030604.9863</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>17340.21</t>
+          <t>20785746211.4736</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>16447.015</t>
+          <t>19818614643.7126</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>17727.206</t>
+          <t>21365703696.848</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>15519.37</t>
+          <t>18334982395.9567</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17496.326</t>
+          <t>20963789151.9294</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>16025.575</t>
+          <t>19010318769.0764</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17780.073</t>
+          <t>21296009431.8871</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>18524.337</t>
+          <t>22419555602.512</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>9027.24</t>
+          <t>9917885874.86298</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>8704.588</t>
+          <t>9613847124.33142</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>8681.275</t>
+          <t>9530886731.65303</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7919.29</t>
+          <t>8650662802.59483</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7722.532</t>
+          <t>8518779970.18503</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>7638.098</t>
+          <t>8388255277.5326</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>6838.202</t>
+          <t>7604465922.82085</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>6720.236</t>
+          <t>7336172565.05747</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>6716.743</t>
+          <t>7371242326.86699</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>7399.785</t>
+          <t>8254322227.61018</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>7579.107</t>
+          <t>8452995720.92208</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>7725.147</t>
+          <t>8664675725.53171</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>8058.756</t>
+          <t>9044033294.92558</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>8826.623</t>
+          <t>10004517222.2994</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>8574.505</t>
+          <t>9585683786.10839</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>7481.846</t>
+          <t>8404888180.12501</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>7308.209</t>
+          <t>8287754181.90252</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>7017.167</t>
+          <t>7989147118.2612</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>6807.452</t>
+          <t>7745799581.96652</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>9459.128</t>
+          <t>11038114608.5164</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>9080.846</t>
+          <t>10482786190.9328</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>10008.398</t>
+          <t>11599126834.784</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>9339.401</t>
+          <t>10786875607.2786</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10186.696</t>
+          <t>11655305335.7584</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>10895.263</t>
+          <t>12569573048.1793</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11282.095</t>
+          <t>12988934444.1443</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>9850.215</t>
+          <t>11074572190.2238</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>162861.358</t>
+          <t>161576906799.664</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>155374.663</t>
+          <t>152832670084.625</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>150825.482</t>
+          <t>148979762381.029</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>148234.743</t>
+          <t>146260851002.967</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>148549.06</t>
+          <t>146569692080.48</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>154255.297</t>
+          <t>152490873493.485</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>154913.247</t>
+          <t>153175998290.251</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>157838.884</t>
+          <t>156061589920.582</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>159027.348</t>
+          <t>157265224884.191</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>166551.036</t>
+          <t>164724238841.749</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>178954.056</t>
+          <t>177031065702.998</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>181316.183</t>
+          <t>179571405424.183</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>181137.353</t>
+          <t>179434256768.118</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>189024.392</t>
+          <t>188067086665.258</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>180467.003</t>
+          <t>179156280789.666</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>183649.957</t>
+          <t>183056886327.865</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>183813.184</t>
+          <t>183861713370.984</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>181364.336</t>
+          <t>181324232257.733</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>187253.257</t>
+          <t>187625670903.748</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>175594.804</t>
+          <t>174615767717.985</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>165898.52</t>
+          <t>164251815579.748</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>143824.301</t>
+          <t>143114730072.302</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>149502.964</t>
+          <t>148606656193.899</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>159949.338</t>
+          <t>158797925071.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>142730.231</t>
+          <t>141774569240.74</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>146223.745</t>
+          <t>145608489614.893</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>149373.283</t>
+          <t>148794088889.952</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>74701.782</t>
+          <t>79133303147.2553</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>22651.077</t>
+          <t>24177892598.5451</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>21571.632</t>
+          <t>23134559694.6877</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>22120.454</t>
+          <t>23726306573.7353</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>22977.015</t>
+          <t>24869515432.8446</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>26193.381</t>
+          <t>28290652436.9984</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>26283.342</t>
+          <t>28424599089.1251</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>26586.712</t>
+          <t>28805605551.3364</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>26545.755</t>
+          <t>28546801188.786</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>30081.083</t>
+          <t>32834299969.0709</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>30958.75</t>
+          <t>33697267043.2802</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>28431.425</t>
+          <t>31148158607.9911</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>29752.068</t>
+          <t>31998348303.5313</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>30688.211</t>
+          <t>33294130381.4271</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>30027.947</t>
+          <t>32736048708.4801</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>28131.652</t>
+          <t>30944861164.3035</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>31641.285</t>
+          <t>34918658541.3879</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>33536.202</t>
+          <t>37046087501.248</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>33974.998</t>
+          <t>37559106168.093</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>28615.564</t>
+          <t>31169297235.9239</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>26908.617</t>
+          <t>29474758362.0053</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>27358.628</t>
+          <t>30026229483.8592</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>25712.626</t>
+          <t>27788318985.9935</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>27133.752</t>
+          <t>29471612813.1753</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>25823.667</t>
+          <t>27950462792.9373</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>26843.391</t>
+          <t>29177411715.5577</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>28465.293</t>
+          <t>31160468932.0707</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3741064.2</t>
+          <t>3396967084024.12</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2279346.173</t>
+          <t>1962789398788.91</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2283615.106</t>
+          <t>2025686388613.37</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2068045.511</t>
+          <t>1850160237740.61</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2138178.139</t>
+          <t>1921103062591.31</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2091425.513</t>
+          <t>1889692318484.57</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2107214.811</t>
+          <t>1904404601449.07</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2133305.551</t>
+          <t>1929598496676.09</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>2210005.352</t>
+          <t>1995902019174.54</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>2386359.994</t>
+          <t>2144757906610.07</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2464345.507</t>
+          <t>2206717964092.73</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2538942.202</t>
+          <t>2273641262615.86</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2626609.972</t>
+          <t>2345454956747.01</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2456078.904</t>
+          <t>2206680983918.54</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2426125.762</t>
+          <t>2177401748911.31</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>2470597.802</t>
+          <t>2217053783164.64</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>2630860.902</t>
+          <t>2370530861542.66</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>2655536.984</t>
+          <t>2404046123061</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>2835402.393</t>
+          <t>2566027368403.55</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>3031748.187</t>
+          <t>2742098168184.91</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>3218726.203</t>
+          <t>2909745100257.19</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>3688896.938</t>
+          <t>3343837281110.86</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>3705438.605</t>
+          <t>3349551944829.03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>3890541.297</t>
+          <t>3535514560729.88</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>4111038.93</t>
+          <t>3716688100745.1</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>4404802.011</t>
+          <t>3993373080273.31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>4679006.949</t>
+          <t>4244868635351.73</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>915.892</t>
+          <t>1147473986.12352</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>783.801</t>
+          <t>989998206.981097</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>718.125</t>
+          <t>905720352.58641</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>734.315</t>
+          <t>917596148.109895</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>792.381</t>
+          <t>1004630570.51707</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>808.632</t>
+          <t>1021926445.00651</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>914.757</t>
+          <t>1165415272.14103</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>913.041</t>
+          <t>1155423704.25409</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>910.474</t>
+          <t>1144684064.0999</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>858.214</t>
+          <t>1073165799.21042</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>881.875</t>
+          <t>1118333617.06794</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>741.98</t>
+          <t>923805544.887432</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>666.206</t>
+          <t>821782392.31363</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>876.608</t>
+          <t>1111554718.81303</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>821.74</t>
+          <t>1032162805.79236</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>822.015</t>
+          <t>1046732423.90066</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>750.59</t>
+          <t>945511564.074656</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>741.727</t>
+          <t>941483756.487986</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>658.328</t>
+          <t>835632234.669899</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>579.344</t>
+          <t>729654588.467901</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>548.861</t>
+          <t>686127180.327539</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>603.398</t>
+          <t>756638487.596398</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>607.257</t>
+          <t>751516040.902647</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>674.502</t>
+          <t>848421103.520351</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>663.879</t>
+          <t>825933219.548791</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>731.607</t>
+          <t>917139268.296021</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>617.614</t>
+          <t>735343013.139555</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14596.018</t>
+          <t>19839255899.1155</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>11665.711</t>
+          <t>15482584868.8047</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>12031.779</t>
+          <t>15983179904.5914</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>11823.191</t>
+          <t>15720402584.0134</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>11718.829</t>
+          <t>15661632010.7135</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>11995.088</t>
+          <t>16239534493.5882</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>12153.136</t>
+          <t>16547704145.5874</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>12221.114</t>
+          <t>16675332601.8651</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>12297.928</t>
+          <t>16687122356.3312</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>12806.671</t>
+          <t>17506671747.4384</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>13643.81</t>
+          <t>18850756593.9684</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>14456.249</t>
+          <t>20139419982.6406</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>13946.313</t>
+          <t>19258184969.5821</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>14931.489</t>
+          <t>20719747907.3105</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>13526.596</t>
+          <t>18359213857.3285</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>14068.688</t>
+          <t>19435563749.545</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>14196.172</t>
+          <t>19663778273.3602</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>13957.672</t>
+          <t>19271168938.0928</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>14018.027</t>
+          <t>19330287564.5177</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>13150.408</t>
+          <t>18169005639.4453</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>12856.224</t>
+          <t>17785360088.4956</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>13660.782</t>
+          <t>18916237488.6766</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>13543.439</t>
+          <t>18524553049.4457</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14692.027</t>
+          <t>20236089593.206</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>15231.428</t>
+          <t>20816002953.28</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16344.146</t>
+          <t>22386659210.9544</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>16465.913</t>
+          <t>22635273726.2806</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>79180.408</t>
+          <t>114602258087.009</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>76651.164</t>
+          <t>105330437117.236</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>75134.759</t>
+          <t>102012011003.399</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>75613.205</t>
+          <t>103330403783.63</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>77900.571</t>
+          <t>107261880115.45</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>79594.657</t>
+          <t>110228897890.693</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>78419.658</t>
+          <t>108393856770.938</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>73964.452</t>
+          <t>101773005082.813</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>77367.348</t>
+          <t>107204844768.821</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>80535.69</t>
+          <t>112240900159.69</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>81495.698</t>
+          <t>113351597932</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>84292.076</t>
+          <t>118155906616.473</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>85817.791</t>
+          <t>120333238377.793</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>90923.818</t>
+          <t>127965007992.268</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>79360.168</t>
+          <t>109143443957.188</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>83258.169</t>
+          <t>116061097708.19</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>86029.768</t>
+          <t>121161343798.66</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>89732.343</t>
+          <t>126016349221.161</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>91339.618</t>
+          <t>128272023115.004</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>82635.638</t>
+          <t>114823537046.642</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>82385.581</t>
+          <t>114883194617.247</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>84126.979</t>
+          <t>117566987358.703</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>81677.002</t>
+          <t>112317986383.31</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>87678.674</t>
+          <t>121480820711.18</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>84218.732</t>
+          <t>116072230785.376</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>90549.15</t>
+          <t>125427933052.688</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>96417.946</t>
+          <t>134870931084.26</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>7820.256</t>
+          <t>11347243802.0056</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>7343.619</t>
+          <t>10185575128.589</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6675.148</t>
+          <t>9117087456.9485</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7000.992</t>
+          <t>9647486813.60862</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>5767.837</t>
+          <t>7936078396.51795</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>7300.397</t>
+          <t>9969788206.43244</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7180.696</t>
+          <t>9821488654.07882</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>6989.676</t>
+          <t>9494648089.62866</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>7059.484</t>
+          <t>9595074605.42514</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>7123.363</t>
+          <t>9769957422.58156</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>7823.694</t>
+          <t>10808838412.7097</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>7867.993</t>
+          <t>10916207460.6465</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>7612.37</t>
+          <t>10489763979.6777</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>9523.602</t>
+          <t>13824545780.1537</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>7916.436</t>
+          <t>11118338167.3919</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>7467.232</t>
+          <t>10593580919.9581</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>8881.99</t>
+          <t>13104101527.3097</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>7843.244</t>
+          <t>11233542306.1187</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>8117.834</t>
+          <t>11654984976.1723</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>6850.945</t>
+          <t>9589143452.08831</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>6739.838</t>
+          <t>9261388443.82494</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>6962.018</t>
+          <t>9694712711.48961</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>6647.357</t>
+          <t>9156567471.94128</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6786.448</t>
+          <t>9347344965.22329</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>6774.986</t>
+          <t>9326901602.60039</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>6452.9</t>
+          <t>8917244414.35239</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>6830.771</t>
+          <t>9505306468.76743</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>61369.004</t>
+          <t>98387013976.9695</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>34954.828</t>
+          <t>52760953658.5498</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>34568.076</t>
+          <t>51832277147.3972</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>36389.682</t>
+          <t>54837517836.894</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>39411.299</t>
+          <t>59868535377.6962</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>43380.17</t>
+          <t>66850886659.0885</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>44818.308</t>
+          <t>69073438713.5004</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>47672.94</t>
+          <t>74290310138.6659</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>47448.736</t>
+          <t>73406020076.9753</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>53161.741</t>
+          <t>83444102750.6387</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>56996.271</t>
+          <t>90274924818.5381</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>60155.553</t>
+          <t>95815445998.2311</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>58710.378</t>
+          <t>91652977283.1768</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>59961</t>
+          <t>93876257464.4987</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>50318.648</t>
+          <t>76777009940.7187</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>46380.087</t>
+          <t>71247544638.83</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>46794.872</t>
+          <t>72355191298.7256</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>44510.99</t>
+          <t>68651839883.8928</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>43868.302</t>
+          <t>68217065714.4966</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>38539.154</t>
+          <t>59032269340.7775</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>36954.542</t>
+          <t>56548842766.2902</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>39020.237</t>
+          <t>59621349030.2047</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>40521.738</t>
+          <t>61033423632.0788</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>41140.72</t>
+          <t>61859664774.5699</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>42878.361</t>
+          <t>64696428755.9992</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>44720.525</t>
+          <t>67921587930.6328</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>44342.436</t>
+          <t>67694202344.8762</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1860.899</t>
+          <t>2755869364.87196</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1878.979</t>
+          <t>2751103371.69079</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1691.274</t>
+          <t>2424349916.72315</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1846.016</t>
+          <t>2662170984.46117</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>1761.881</t>
+          <t>2581640069.89023</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2138.028</t>
+          <t>3299724715.46642</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1938.697</t>
+          <t>2924054703.6615</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1829.984</t>
+          <t>2713196769.75891</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>1736.916</t>
+          <t>2590118973.09673</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>1870.101</t>
+          <t>2819118291.98534</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>1856.972</t>
+          <t>2799164293.29329</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>1994.711</t>
+          <t>3009080887.97734</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>1884.174</t>
+          <t>2755840541.69627</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>1978.697</t>
+          <t>2934393701.89708</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>1576.766</t>
+          <t>2250322144.19318</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1755.021</t>
+          <t>2571032963.58824</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1581.475</t>
+          <t>2334533610.59422</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>1738.011</t>
+          <t>2539207357.59107</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>1710.062</t>
+          <t>2495941121.68389</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>1641.268</t>
+          <t>2385605769.27635</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1653.736</t>
+          <t>2417045950.81807</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>1558.317</t>
+          <t>2252939202.26466</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>1577.361</t>
+          <t>2257322873.47809</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>1773.563</t>
+          <t>2577969098.18575</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>1844.347</t>
+          <t>2677384283.66219</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>1958.007</t>
+          <t>2830264254.92</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>1991.612</t>
+          <t>2932237128.10686</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11811.881</t>
+          <t>29452806769.1077</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6318.734</t>
+          <t>12059740672.5266</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>6420.371</t>
+          <t>12328850911.1419</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>7048.256</t>
+          <t>13378137200.5324</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7519.001</t>
+          <t>14675952481.7169</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>8073.594</t>
+          <t>16011092652.6449</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>7671.68</t>
+          <t>15077298023.7801</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7364.462</t>
+          <t>14408703447.7136</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>7363.533</t>
+          <t>14175816970.3644</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>7784.687</t>
+          <t>15384303410.6285</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>7714.459</t>
+          <t>15183817964.4522</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>7934.601</t>
+          <t>15474601853.8489</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>7764.417</t>
+          <t>15042968048.6461</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>8336.569</t>
+          <t>16613580459.0235</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>6711.282</t>
+          <t>13031695887.0553</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>6721.596</t>
+          <t>12847737807.4774</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>7121.093</t>
+          <t>13995546978.0615</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>6685.02</t>
+          <t>12799624816.5487</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>6864.66</t>
+          <t>13068773029.3715</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>6152.461</t>
+          <t>11747641619.4506</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>5842.436</t>
+          <t>11083969265.438</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>5735.033</t>
+          <t>10846648602.4578</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>5709.487</t>
+          <t>10665117625.5643</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>5910.471</t>
+          <t>10950735042.4107</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>6133.602</t>
+          <t>11322185109.1317</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>6137.64</t>
+          <t>11419097453.4505</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>6148.43</t>
+          <t>11497958605.9846</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>73363.653</t>
+          <t>152929345405.747</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>56045.557</t>
+          <t>108131079139.158</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>52151.15</t>
+          <t>93818489147.0615</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>55083.105</t>
+          <t>103393024093.923</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>54294.43</t>
+          <t>102106065772.43</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>59013.613</t>
+          <t>113354249272.001</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>58887.967</t>
+          <t>112988209215.502</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>57627.063</t>
+          <t>108855676719.363</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>55129.322</t>
+          <t>102876991363.395</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>59140.539</t>
+          <t>114306989293.95</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>62458.635</t>
+          <t>119766686613.776</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>60564.343</t>
+          <t>122296672413.899</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>58671.026</t>
+          <t>120099809698.357</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>63772.226</t>
+          <t>103337812158.714</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>53000.009</t>
+          <t>99777849958.5263</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>54080.794</t>
+          <t>101902101835.006</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>54884.204</t>
+          <t>104718092039.868</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>55308.468</t>
+          <t>103519685898.928</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>58649.437</t>
+          <t>112469287846.215</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>48166.23</t>
+          <t>88952103372.0912</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>46207.374</t>
+          <t>84923370703.1724</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>47471.813</t>
+          <t>89175057941.2603</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>44629.709</t>
+          <t>80174555623.7621</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>47665.988</t>
+          <t>86497277764.4693</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>46738.85</t>
+          <t>84514460331.9083</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>47106.793</t>
+          <t>85416402565.2377</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>49595.376</t>
+          <t>91953312203.9163</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>83228.432</t>
+          <t>92422479054.8985</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>57558.766</t>
+          <t>60708700808.3595</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>60193.547</t>
+          <t>63338322656.4841</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>59608.302</t>
+          <t>63002567819.4781</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>60762.809</t>
+          <t>64530940133.6958</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>60326.032</t>
+          <t>64393916055.8921</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>58912.199</t>
+          <t>62439981535.744</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>60519.997</t>
+          <t>64627274958.7291</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>59544.505</t>
+          <t>63045848250.3366</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>68264.366</t>
+          <t>73760356588.6033</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>69533.071</t>
+          <t>75016145599.493</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>65656.076</t>
+          <t>70183780303.7178</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>60667.395</t>
+          <t>63817067878.5147</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>63057.942</t>
+          <t>66665492861.3724</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>60291.25</t>
+          <t>63641617702.0334</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>57265.212</t>
+          <t>60440569238.7562</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>57572.25</t>
+          <t>60903407733.8267</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>61260.535</t>
+          <t>65493728355.0099</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>61768.593</t>
+          <t>65779760844.2134</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>55852.219</t>
+          <t>58861953449.8094</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>57553.201</t>
+          <t>60305516867.0454</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>64098.029</t>
+          <t>66764614788.4058</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>56341.173</t>
+          <t>58620512928.0061</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>56334.691</t>
+          <t>58987520674.8422</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>58011.273</t>
+          <t>60507550710.2616</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>60657.36</t>
+          <t>63456620623.8165</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>62328.425</t>
+          <t>65439223642.255</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8082.07</t>
+          <t>16565341852.0092</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>10273.513</t>
+          <t>19797873933.1133</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>9177.289</t>
+          <t>17103021444.8707</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>9193.266</t>
+          <t>17002429996.462</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>9818.265</t>
+          <t>18369809937.347</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>10257.811</t>
+          <t>19228802799.3336</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10636.215</t>
+          <t>20170284213.3114</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>10645.582</t>
+          <t>20245462403.9369</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>10475.295</t>
+          <t>19786343597.2439</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>10706.12</t>
+          <t>20072192069.4573</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>10122.926</t>
+          <t>18809905654.8416</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>10513.113</t>
+          <t>19492020129.1828</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>10722.121</t>
+          <t>19719170914.6089</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>10657.322</t>
+          <t>19585384685.1355</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>9282.084</t>
+          <t>16821939810.4021</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>9498.93</t>
+          <t>17276392934.6958</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>8759.345</t>
+          <t>15805258398.0836</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>8339.01</t>
+          <t>15032854567.8345</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>7491.323</t>
+          <t>13615293779.3275</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>6535.836</t>
+          <t>11681854479.6268</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>5758.386</t>
+          <t>10366126624.8212</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>5828.647</t>
+          <t>10515807565.2229</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>5597.415</t>
+          <t>9921285371.34803</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6212.154</t>
+          <t>10909377500.9206</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>6331.976</t>
+          <t>11140303769.4605</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>6556.062</t>
+          <t>11562028981.4351</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>6349.518</t>
+          <t>11165740524.3527</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10416.59</t>
+          <t>18310731654.9824</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>9595.055</t>
+          <t>16795341948.0362</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>8965.09</t>
+          <t>15227007788.2012</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9529.591</t>
+          <t>16360484523.5691</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>10323.711</t>
+          <t>17907196107.3889</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>10334.353</t>
+          <t>17759498954.5712</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11159.258</t>
+          <t>19500010778.2296</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>11415.803</t>
+          <t>19647843639.5391</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>11228.459</t>
+          <t>19338430102.1065</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>11976.54</t>
+          <t>20773840706.4628</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>11928.654</t>
+          <t>20739909581.7629</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>11532.048</t>
+          <t>19966914657.5585</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>11159.392</t>
+          <t>18877962453.4454</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>11853.707</t>
+          <t>20238244554.6394</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>10228.601</t>
+          <t>17110014606.8953</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>10160.378</t>
+          <t>17122944226.9701</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>10245.671</t>
+          <t>17288107830.5803</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>9375.832</t>
+          <t>15614022294.8888</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>9385.502</t>
+          <t>15647911592.7593</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>9146.515</t>
+          <t>15303668727.157</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>9229.367</t>
+          <t>15389269738.8863</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>9963.489</t>
+          <t>16687834624.9416</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>10042.375</t>
+          <t>16703121989.8765</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11319.22</t>
+          <t>18965115157.902</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>11391.021</t>
+          <t>18833536893.8957</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12323.192</t>
+          <t>20507689961.6555</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>12266.532</t>
+          <t>20358869065.6776</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>2692249.915</t>
+          <t>2634597316590.8</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1040510.694</t>
+          <t>1019746310251.64</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1086631.31</t>
+          <t>1064797621977.38</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1055400.467</t>
+          <t>1035151478574.62</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>1071488.144</t>
+          <t>1051467512959.6</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>1123254.871</t>
+          <t>1101616011505.04</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1229400.792</t>
+          <t>1204665532739.9</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1216559.451</t>
+          <t>1193445526368.86</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>1220882.235</t>
+          <t>1196225026222.03</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1282269.268</t>
+          <t>1257792269878.75</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1286350.813</t>
+          <t>1262728333192.4</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1282708.353</t>
+          <t>1258910817068.14</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1261298.451</t>
+          <t>1237120945813.79</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1322682.1</t>
+          <t>1298761923113.03</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1327988.954</t>
+          <t>1304083180779.16</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1332862.127</t>
+          <t>1309255860346.24</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1323609.394</t>
+          <t>1302500855625.83</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>1320611.76</t>
+          <t>1299785806753.11</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>1272776.675</t>
+          <t>1254690449144.01</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>1230531.095</t>
+          <t>1212840061702.31</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>1308175.458</t>
+          <t>1289196514957.73</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>1576787.671</t>
+          <t>1551072342662.37</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>1682391.918</t>
+          <t>1654594560626.66</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>1889802.486</t>
+          <t>1859513441470.03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>1840962.431</t>
+          <t>1809949072968.38</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2054418.208</t>
+          <t>2021048017159.93</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>2204969.305</t>
+          <t>2169285680541.81</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>356919.936</t>
+          <t>421243436191.943</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>177677.661</t>
+          <t>211025823405.305</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>193600.965</t>
+          <t>230503967916.115</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>185464.456</t>
+          <t>218730521365.515</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>191716.885</t>
+          <t>228183654120.23</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>181439.833</t>
+          <t>213436119737.708</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>195043.329</t>
+          <t>232075820868.954</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>208239.198</t>
+          <t>249891943760.54</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>213510.415</t>
+          <t>256961285066.19</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>205853.477</t>
+          <t>247443553149.183</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>228832.192</t>
+          <t>274640316447.368</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>238570.186</t>
+          <t>286333520091.803</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>230092.542</t>
+          <t>274545067274.857</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>237705.958</t>
+          <t>285719105334.514</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>268656.96</t>
+          <t>325138549861.16</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>254849.781</t>
+          <t>306780256825.065</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>258871.839</t>
+          <t>311415304130.989</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>240876.762</t>
+          <t>290276720557.899</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>250181.69</t>
+          <t>300717592631.435</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>255492.061</t>
+          <t>305894427326.011</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>222642.697</t>
+          <t>265767367436.847</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>273577.186</t>
+          <t>325847750476.461</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>285748.932</t>
+          <t>338692724081.579</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>306075.788</t>
+          <t>363640780999.9</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>289989.746</t>
+          <t>343932281936.628</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>329884.262</t>
+          <t>392014148587.66</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>347139.516</t>
+          <t>412664893501.831</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>7268.346</t>
+          <t>10482195823.2659</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4060.48</t>
+          <t>6371830251.27398</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>4166.966</t>
+          <t>6422517827.47247</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4420.822</t>
+          <t>6768082103.27941</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>4617.124</t>
+          <t>6943013378.44475</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>5312.787</t>
+          <t>8030323484.26126</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>5305.014</t>
+          <t>7986315869.54898</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>4916.627</t>
+          <t>7195940872.32701</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>4688.033</t>
+          <t>6860337034.30539</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>5409.47</t>
+          <t>7972897555.07112</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>6088.031</t>
+          <t>8944854359.55774</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>6329.19</t>
+          <t>9408471691.59139</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>5963.367</t>
+          <t>8624747374.5525</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>6461.351</t>
+          <t>9627738768.18106</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>4860.65</t>
+          <t>7104384193.51475</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>4054.122</t>
+          <t>5826406740.79282</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>3788.631</t>
+          <t>5446348248.55798</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>3884.285</t>
+          <t>5647779750.02806</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>4195.656</t>
+          <t>6207572332.61485</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>4142.227</t>
+          <t>5976402930.1242</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>5452.664</t>
+          <t>8190583958.6214</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>6675.237</t>
+          <t>9773539643.00387</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>6473.412</t>
+          <t>9065625263.89013</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>7881.028</t>
+          <t>11679080089.7255</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>8577.205</t>
+          <t>12525512584.568</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>9723.635</t>
+          <t>14304585931.6387</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>11333.006</t>
+          <t>16755139149.9895</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>61605.853</t>
+          <t>91731380591.5918</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>62804.581</t>
+          <t>87227109105.4477</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>63342.402</t>
+          <t>87325856544.0257</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>63280.089</t>
+          <t>87248229854.8415</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>66280.083</t>
+          <t>92143536276.4102</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>66310.221</t>
+          <t>92630013850.0625</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>67583.399</t>
+          <t>94498057324.0102</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>67773.208</t>
+          <t>94175846173.1156</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>61423.667</t>
+          <t>85194424535.2055</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>72600.968</t>
+          <t>101462361105.428</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>73171.918</t>
+          <t>102284766996.96</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>76129.163</t>
+          <t>107389583054.926</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>72038.524</t>
+          <t>100259419703.289</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>76548.237</t>
+          <t>107605573013.721</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>67812.801</t>
+          <t>94104295885.0435</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>68134.428</t>
+          <t>95782825086.4154</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>70226.364</t>
+          <t>99505136377.7639</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>67507.65</t>
+          <t>94987246043.4518</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>66305.628</t>
+          <t>93634828891.4925</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>56089.603</t>
+          <t>78358708130.4546</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>53353.402</t>
+          <t>74286757805.8834</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>54898.081</t>
+          <t>76898275413.1723</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>52448.308</t>
+          <t>72436811063.7545</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>55538.749</t>
+          <t>77395274506.5732</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>55038.861</t>
+          <t>76509440038.4363</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>55406.31</t>
+          <t>77366771722.516</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>56276.203</t>
+          <t>79171900172.7954</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>469931.351</t>
+          <t>486480779362.013</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>215049.25</t>
+          <t>207499925761.946</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>217652.102</t>
+          <t>208449872953.665</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>196294.649</t>
+          <t>187484627058.431</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>199707.194</t>
+          <t>192320826438.498</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>204193.465</t>
+          <t>197199182420.469</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>210279.885</t>
+          <t>204180322400.862</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>203744.64</t>
+          <t>198157713658.555</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>190026.565</t>
+          <t>182539612517.585</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>201900.432</t>
+          <t>196445010654.637</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>214529.185</t>
+          <t>208982777364.177</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>199638.379</t>
+          <t>194190944814.576</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>186184.631</t>
+          <t>176916381125.415</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>202514.532</t>
+          <t>196703184183.443</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>178370.143</t>
+          <t>172266687845.611</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>186593.415</t>
+          <t>181148247828.662</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>193952.764</t>
+          <t>189353226514.288</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>188225.343</t>
+          <t>184172553263.607</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>185777.16</t>
+          <t>181543592248.129</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>151743.019</t>
+          <t>150321314186.451</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>151521.897</t>
+          <t>150002121583.34</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>173757.19</t>
+          <t>172031570299.638</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>167391.922</t>
+          <t>165091893532.556</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>175413.42</t>
+          <t>174383125693.791</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>171666.925</t>
+          <t>169875228524.936</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>181465.689</t>
+          <t>180363948180.092</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>170038.513</t>
+          <t>170099129587.366</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>128018.605</t>
+          <t>144518546457.536</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>67417.198</t>
+          <t>72874353958.4666</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>73608.69</t>
+          <t>78832686723.8581</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>62454.673</t>
+          <t>67001278751.9562</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>65100.428</t>
+          <t>71282475230.1916</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>73633.134</t>
+          <t>81019303300.3362</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>73893.491</t>
+          <t>80936699368.7913</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>77598.177</t>
+          <t>85679841447.1374</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>73299.362</t>
+          <t>78927607259.6444</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>89527.747</t>
+          <t>98986981085.1174</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>93493.176</t>
+          <t>102699746351.382</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>93688.608</t>
+          <t>102496229426.36</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>90355.466</t>
+          <t>96764012455.6199</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>98700.988</t>
+          <t>108637692092.272</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>87506.358</t>
+          <t>96190695280.7865</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>89846.238</t>
+          <t>99034594527.6925</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>100399.176</t>
+          <t>111722961618.011</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>95954.058</t>
+          <t>106656436556.623</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>100889.499</t>
+          <t>111911100469.852</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>97591.951</t>
+          <t>108656884469.26</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>110104.221</t>
+          <t>122514652870.166</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>121049.575</t>
+          <t>134584205315.303</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>129304.716</t>
+          <t>142960429044.673</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>138620.919</t>
+          <t>154441924778.276</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>135857.3</t>
+          <t>150583898845.341</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>141037.764</t>
+          <t>157364988204.135</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>147716.555</t>
+          <t>165672530394.769</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4179.704</t>
+          <t>5138275881.92849</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3657.313</t>
+          <t>4278021980.04339</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4352.521</t>
+          <t>5350199212.91688</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>4082.648</t>
+          <t>4931556369.92523</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>4133.358</t>
+          <t>5011495896.31602</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>4052.226</t>
+          <t>4936822485.74642</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3888.63</t>
+          <t>4769692188.79169</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>3691.741</t>
+          <t>4497318414.65623</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>3753.632</t>
+          <t>4571241751.77349</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>3814.839</t>
+          <t>4654223846.42954</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>3528.47</t>
+          <t>4284171498.93259</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>3579.202</t>
+          <t>4320918144.91742</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>3381.142</t>
+          <t>4053428082.62118</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>3694.491</t>
+          <t>4467238696.23129</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>3196.751</t>
+          <t>3808242564.34972</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>3014.043</t>
+          <t>3636667999.67068</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>2916.322</t>
+          <t>3526352080.45967</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>3093.059</t>
+          <t>3775652857.26053</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>2971.015</t>
+          <t>3559963565.6508</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>2815.792</t>
+          <t>3384853749.11332</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>2927.919</t>
+          <t>3515603954.83678</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>3023.36</t>
+          <t>3639830054.59249</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>3146.34</t>
+          <t>3791515900.02053</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>3451.675</t>
+          <t>4180467814.10031</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>3707.704</t>
+          <t>4489179373.04388</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>3892.33</t>
+          <t>4714368580.52689</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>3643.763</t>
+          <t>4346208312.73244</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>412.466</t>
+          <t>470215459.915634</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>555.552</t>
+          <t>691218431.335494</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>525.149</t>
+          <t>651192465.043526</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>604.026</t>
+          <t>750505024.782176</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>727.919</t>
+          <t>926636744.340212</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>778.851</t>
+          <t>993454970.702891</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>746.939</t>
+          <t>961325656.417766</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>757.805</t>
+          <t>976577739.028218</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>744.05</t>
+          <t>942098941.646528</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1000.282</t>
+          <t>1279818925.36748</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1015.232</t>
+          <t>1308657961.4149</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>983.752</t>
+          <t>1266107827.65948</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>910.232</t>
+          <t>1154228877.12392</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>1160.074</t>
+          <t>1495977483.70334</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>1048.674</t>
+          <t>1350145690.42884</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1156.468</t>
+          <t>1480269989.5475</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1189.708</t>
+          <t>1543148898.98803</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1233.803</t>
+          <t>1606846361.57933</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>1502.157</t>
+          <t>1954729950.33548</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>1730.063</t>
+          <t>2277575677.92599</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>2056.913</t>
+          <t>2727747785.73854</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>2313.19</t>
+          <t>3052000334.02677</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>1691.888</t>
+          <t>2185916762.12589</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>2066.424</t>
+          <t>2708223950.17766</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>1738.154</t>
+          <t>2249602543.68073</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2125.827</t>
+          <t>2788604996.49924</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>2452.319</t>
+          <t>3244372664.15021</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2648.059</t>
+          <t>3041555384.6184</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2542.209</t>
+          <t>2767972070.11735</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2704.972</t>
+          <t>3059529501.44641</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2561.785</t>
+          <t>2907948123.75234</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2795.749</t>
+          <t>3281549967.85581</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2897.86</t>
+          <t>3384478992.77658</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2707.84</t>
+          <t>3162675772.806</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>2709.126</t>
+          <t>3105303241.27577</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>2686.644</t>
+          <t>3084592180.17925</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>2966.754</t>
+          <t>3425066693.00766</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>2931.368</t>
+          <t>3351408347.58406</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>2937.403</t>
+          <t>3366793296.25084</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2993.724</t>
+          <t>3415923582.2321</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>2947.867</t>
+          <t>3410202945.23666</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2605.647</t>
+          <t>2994677430.44972</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>2143.182</t>
+          <t>2459177632.95482</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>2148.327</t>
+          <t>2522472477.23368</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>2205.401</t>
+          <t>2578549449.11944</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>2072.214</t>
+          <t>2389150272.49899</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>2142.25</t>
+          <t>2467685881.37547</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>2084.809</t>
+          <t>2451726377.9651</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>2183.742</t>
+          <t>2518491561.53488</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2148.381</t>
+          <t>2494290187.30797</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>2503.177</t>
+          <t>2904878432.81127</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2517.726</t>
+          <t>2914130368.09733</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2582.941</t>
+          <t>3016646261.98051</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>2531.142</t>
+          <t>2909782702.25777</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>129934.245</t>
+          <t>128694081616.882</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>61609.286</t>
+          <t>60994917953.879</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>67328.523</t>
+          <t>66727107392.5173</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>73859.581</t>
+          <t>73195520428.8033</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>71893.988</t>
+          <t>71482028972.7102</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>78014.608</t>
+          <t>77743985186.7404</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>77101.341</t>
+          <t>77191497545.3424</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>74588.337</t>
+          <t>74710370718.5699</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>74305.814</t>
+          <t>74063604392.4256</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>73875.373</t>
+          <t>74004709413.7128</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>75732.143</t>
+          <t>75823262542.2051</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>76536.54</t>
+          <t>76735189644.5972</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>75754.032</t>
+          <t>75462980037.8306</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>79013.697</t>
+          <t>79199533410.6709</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>79716.012</t>
+          <t>79672064448.8337</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>81182.072</t>
+          <t>81265188061.621</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>84300.952</t>
+          <t>84527069824.0737</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>88131.027</t>
+          <t>88365737353.3777</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>93394.714</t>
+          <t>93428753538.7746</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>94132.593</t>
+          <t>93771775488.3795</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>107276.952</t>
+          <t>107008701119.281</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>100830.707</t>
+          <t>100659356818.268</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>91372.506</t>
+          <t>91355189991.6672</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>106772.656</t>
+          <t>106453877679.428</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>108213.938</t>
+          <t>107553162727.586</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>116671.706</t>
+          <t>116131647211.682</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>128768.765</t>
+          <t>128055284398.027</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>610.046</t>
+          <t>712255416.876192</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>361.737</t>
+          <t>441962065.846939</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>357.103</t>
+          <t>426192544.564556</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>370.661</t>
+          <t>443628365.231643</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>473.437</t>
+          <t>580261511.076118</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>618.62</t>
+          <t>763137525.071547</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>549.191</t>
+          <t>669290843.377071</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>470.182</t>
+          <t>580331524.091114</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>534.317</t>
+          <t>649325007.594537</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>542.021</t>
+          <t>661363850.598821</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>498.884</t>
+          <t>603464388.108408</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>523.883</t>
+          <t>640568680.194507</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>510.481</t>
+          <t>626980284.45388</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>512.513</t>
+          <t>624821278.315237</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>590.854</t>
+          <t>722003860.482977</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>514.918</t>
+          <t>626652943.766365</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>439.374</t>
+          <t>530361819.650759</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>448.682</t>
+          <t>558467014.163435</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>546.623</t>
+          <t>678747879.567032</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>529.728</t>
+          <t>643176930.83473</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>672.601</t>
+          <t>836903298.700707</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>507.314</t>
+          <t>606885965.750528</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>663.963</t>
+          <t>808656311.290475</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>637.611</t>
+          <t>760586124.948368</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>634.637</t>
+          <t>739744843.60048</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>659.286</t>
+          <t>772371721.598068</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>660.452</t>
+          <t>772568421.07648</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>26712.774</t>
+          <t>31959228422.6614</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>24758.279</t>
+          <t>29640661621.2697</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>23010.684</t>
+          <t>27522466183.2844</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>23294.301</t>
+          <t>27931093192.8534</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>25915.528</t>
+          <t>31414888326.048</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>26036.773</t>
+          <t>31452677565.8593</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>27154.43</t>
+          <t>33052550819.03</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>26467.357</t>
+          <t>32115153965.4911</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>24908.617</t>
+          <t>30014952573.1964</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>27203.643</t>
+          <t>33061623860.7299</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>25863.992</t>
+          <t>31422585862.4681</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>26882.421</t>
+          <t>32706858221.9715</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>24605.94</t>
+          <t>29470142459.8828</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>28290.092</t>
+          <t>34420777815.1975</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>26051.037</t>
+          <t>31332700209.7526</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>26452.143</t>
+          <t>31994560080.9543</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>23993.639</t>
+          <t>29230667349.8845</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>27853.314</t>
+          <t>34143595753.9709</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>29801.245</t>
+          <t>36607601554.8589</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>23533.362</t>
+          <t>28828685390.3857</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>21760.607</t>
+          <t>26352658947.4947</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>24911.13</t>
+          <t>30625959825.3725</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>22112.491</t>
+          <t>26669829688.8433</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>24622.497</t>
+          <t>30003539516.8878</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>23830.21</t>
+          <t>28852108128.7036</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>26672.187</t>
+          <t>32499312598.1863</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>29187.878</t>
+          <t>36153151892.9953</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>45233.09</t>
+          <t>48155963922.6412</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>45498.657</t>
+          <t>50258384613.9182</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>42283.828</t>
+          <t>45922022207.0548</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>40886.052</t>
+          <t>44299052203.3377</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>41616.281</t>
+          <t>45396955094.8212</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>40757.169</t>
+          <t>44873072130.8749</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>40467.314</t>
+          <t>44485707189.7988</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>39058.97</t>
+          <t>42990985157.3418</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>38025.489</t>
+          <t>41910049091.8499</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>38560.054</t>
+          <t>42683674243.6317</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>38719.387</t>
+          <t>42923974998.0913</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>39141.108</t>
+          <t>43412754049.2422</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>40014.891</t>
+          <t>44167226472.9385</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>42277.715</t>
+          <t>46996773294.9818</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>39816.802</t>
+          <t>43716788338.9336</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>40363.539</t>
+          <t>44715386901.7844</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>40722.006</t>
+          <t>45319879912.5448</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>39119.432</t>
+          <t>43396930867.5951</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>39376.539</t>
+          <t>43751378760.9222</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>39383.984</t>
+          <t>43820489550.5912</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>41051.386</t>
+          <t>45751538345.6745</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>40795.76</t>
+          <t>45630068164.2347</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>38877.128</t>
+          <t>43250520157.7347</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>45086.56</t>
+          <t>50375166583.2518</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>45264.628</t>
+          <t>50581681638.384</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>49623.251</t>
+          <t>55717931389.5413</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>49676.155</t>
+          <t>55581214512.6075</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>13653.546</t>
+          <t>14448508897.6361</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>14372.857</t>
+          <t>14736196794.097</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>12556.371</t>
+          <t>12721199863.0296</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>12720.725</t>
+          <t>12966544412.059</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>13880.743</t>
+          <t>14082814859.4939</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>13882.036</t>
+          <t>14176330507.1873</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>13611.376</t>
+          <t>13886127727.5291</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>13521.414</t>
+          <t>13747728451.3924</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>13018.249</t>
+          <t>13170078988.6833</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>13456.874</t>
+          <t>13703158800.3612</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>13451.984</t>
+          <t>13703127779.5713</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>12903.768</t>
+          <t>13158160010.5654</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>12698.342</t>
+          <t>12845931036.8144</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>13618.466</t>
+          <t>13960315607.8573</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>12045.473</t>
+          <t>12180859606.0085</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>11736.105</t>
+          <t>11920000787.2296</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>12028.921</t>
+          <t>12293089429.9075</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>11410.674</t>
+          <t>11629257435.0131</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>11613.93</t>
+          <t>12046800905.6614</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>10064.334</t>
+          <t>10238675151.2234</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>9724.689</t>
+          <t>9835943504.49207</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>9877.599</t>
+          <t>9979196870.53994</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>10010.15</t>
+          <t>10116109149.0222</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11124.48</t>
+          <t>11180395110.3098</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>10700.661</t>
+          <t>10857743304.3196</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11247.805</t>
+          <t>11455624876.6454</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>11093.2</t>
+          <t>11274333424.4597</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>28870.013</t>
+          <t>26455423816.8669</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>27572.874</t>
+          <t>25275299353.6718</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>28322.976</t>
+          <t>26332328382.8777</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>33356.996</t>
+          <t>30815774701.1297</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>32773.958</t>
+          <t>30296050797.673</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>32968.439</t>
+          <t>30514869770.4891</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>32196.944</t>
+          <t>30011810296.7868</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>31326.822</t>
+          <t>29261527808.7452</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27233.566</t>
+          <t>25404490576.455</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>27325.576</t>
+          <t>25596809607.327</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>26999.045</t>
+          <t>25340851090.0758</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>24705.083</t>
+          <t>23161297713.2389</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>25380.827</t>
+          <t>23781742663.7589</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>26512.848</t>
+          <t>24824673936.7838</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>24427.004</t>
+          <t>22867472245.4795</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>24347.085</t>
+          <t>22964362181.087</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>24166.378</t>
+          <t>22925986318.3759</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>25149.882</t>
+          <t>23778840672.3513</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>23664.099</t>
+          <t>22451702052.6884</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>25893.363</t>
+          <t>24448710240.5601</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>24342.015</t>
+          <t>23073622393.0735</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>26891.336</t>
+          <t>25521750180.5395</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>26282.873</t>
+          <t>24803828411.3869</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>28476.196</t>
+          <t>27102344899.986</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>30865.995</t>
+          <t>29379854145.1796</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>34179.586</t>
+          <t>32409823419.4005</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>32409.134</t>
+          <t>30663161852.6597</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>173547.693</t>
+          <t>229000606927.982</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>124634.05</t>
+          <t>147420609038.195</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>138815.116</t>
+          <t>172115591379.505</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>120218.104</t>
+          <t>147151148171.04</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>124242.849</t>
+          <t>153248436084.411</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>137252.761</t>
+          <t>166863650595.304</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>144356.866</t>
+          <t>177405298159.858</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>124470.952</t>
+          <t>150691746068.24</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>131398.163</t>
+          <t>160470321633.342</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>137872.689</t>
+          <t>169209494897.014</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>129732.237</t>
+          <t>159396564438.212</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>138346.73</t>
+          <t>170020101539.868</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>134533.424</t>
+          <t>164661028108.235</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>145124.35</t>
+          <t>180668049292.768</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>133982.015</t>
+          <t>167257359517.265</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>134276.078</t>
+          <t>166634721246.058</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>146174.18</t>
+          <t>184052135020.237</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>132137.281</t>
+          <t>166617304126.971</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>143653.904</t>
+          <t>179833580374.37</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>142818.71</t>
+          <t>177969688143.988</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>119544.788</t>
+          <t>147489289175.11</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>97299.25</t>
+          <t>120549718580.781</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>99397.778</t>
+          <t>123595827606.353</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>112955.188</t>
+          <t>139802459983.087</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>118145.9</t>
+          <t>147260137748.7</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>124162.506</t>
+          <t>154780504688.654</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>124924.77</t>
+          <t>156118635902.334</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>15694.668</t>
+          <t>16060048009.4891</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>5336.336</t>
+          <t>5054956313.50061</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>6697.986</t>
+          <t>6568321997.59501</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>6412.594</t>
+          <t>6194025995.65292</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6090.89</t>
+          <t>5853039434.39017</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>6260.341</t>
+          <t>6116243485.71758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6313.073</t>
+          <t>6180347473.97964</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>6104.722</t>
+          <t>5949158289.67702</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>6192.551</t>
+          <t>6043655877.8913</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>6204.186</t>
+          <t>6167585443.3634</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>6268.942</t>
+          <t>6255481659.53066</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>6696.171</t>
+          <t>6765887508.30455</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>6729.945</t>
+          <t>6761543800.24413</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>7536.595</t>
+          <t>7664091888.1906</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>7337.11</t>
+          <t>7359501396.71916</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>6537.737</t>
+          <t>6535662820.55852</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>6726.674</t>
+          <t>6878857366.05226</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>6792.766</t>
+          <t>6918379956.57999</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>6998.271</t>
+          <t>7162283115.49403</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>6748.617</t>
+          <t>6862151434.37638</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>6928.145</t>
+          <t>7050180315.24271</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>7466.637</t>
+          <t>7644199000.03888</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>6966.74</t>
+          <t>7106008491.03779</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>7976.791</t>
+          <t>8231372234.97995</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>8080.162</t>
+          <t>8269975553.67228</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>8552.185</t>
+          <t>8835235033.41149</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>8469.908</t>
+          <t>8579413260.9146</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>3007.561</t>
+          <t>2978256834.72669</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>3260.111</t>
+          <t>3301321244.30366</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2903.243</t>
+          <t>2858313212.13252</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2736.409</t>
+          <t>2676123810.49865</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2844.572</t>
+          <t>2811098657.47884</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2832.385</t>
+          <t>2804089332.62444</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>2835.202</t>
+          <t>2801748125.13946</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>2812.893</t>
+          <t>2768685096.5985</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>2852.065</t>
+          <t>2797698348.82986</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2834.32</t>
+          <t>2822129394.60027</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>3060.266</t>
+          <t>3076676745.30912</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>3245.293</t>
+          <t>3295297939.60543</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>3128.756</t>
+          <t>3160142600.12633</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>3295.296</t>
+          <t>3309332116.03187</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2912.744</t>
+          <t>2870564019.47026</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>2847.413</t>
+          <t>2851953220.23997</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>2929.234</t>
+          <t>2999833425.81043</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>2786.415</t>
+          <t>2829637637.35225</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>2781.246</t>
+          <t>2837907718.12603</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>2616.722</t>
+          <t>2649308558.26144</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>2497.865</t>
+          <t>2528789678.58411</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>2711.566</t>
+          <t>2785843048.68369</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2828.563</t>
+          <t>2916557424.80758</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>3012.898</t>
+          <t>3147932828.65583</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>3118.386</t>
+          <t>3181948409.78592</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>3342.072</t>
+          <t>3492636628.14916</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>3078.252</t>
+          <t>3131556345.27478</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>18777.75</t>
+          <t>18924770147.5264</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>9679.56</t>
+          <t>9095064649.35671</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>9363.922</t>
+          <t>8791946655.7474</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>9829.145</t>
+          <t>9262020785.82598</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>9433.18</t>
+          <t>8995497423.76662</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10883.779</t>
+          <t>10376908828.3959</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10734.728</t>
+          <t>10219474359.4682</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>10471.719</t>
+          <t>10014145123.165</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>10254.972</t>
+          <t>9698471835.79372</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>10844.988</t>
+          <t>10406480332.1102</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>11204.268</t>
+          <t>10805406991.4911</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>11350.154</t>
+          <t>10998407906.6884</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>11168.922</t>
+          <t>10679625641.2615</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>11468.301</t>
+          <t>11080322687.8374</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>10292.197</t>
+          <t>9779581872.10594</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>9875.212</t>
+          <t>9439841724.8212</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>10884.675</t>
+          <t>10547925423.7157</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>10734.344</t>
+          <t>10367012669.1204</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>10723.194</t>
+          <t>10345290760.9526</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>10191.799</t>
+          <t>9788793804.03155</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>9736.97</t>
+          <t>9345938222.25205</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>9416.793</t>
+          <t>9033510755.72024</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>8818.483</t>
+          <t>8445830700.65372</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>8852.077</t>
+          <t>8493461015.43076</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>8649.786</t>
+          <t>8295588469.00564</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>8949.433</t>
+          <t>8628683580.38796</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>9362.081</t>
+          <t>9085784380.48797</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>60398.763</t>
+          <t>84355070124.2299</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>60049.814</t>
+          <t>82636592394.0102</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>57439.722</t>
+          <t>77673498826.5697</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>57559.308</t>
+          <t>78217361862.4237</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>61985.948</t>
+          <t>87365141199.2437</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>63125.736</t>
+          <t>86878475114.3107</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>61485.23</t>
+          <t>84603453674.5853</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>69612.078</t>
+          <t>96596366494.8995</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>66700.621</t>
+          <t>92154869448.2911</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>73837.366</t>
+          <t>104114612200.51</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>76164.704</t>
+          <t>106974514868.056</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>77147.68</t>
+          <t>109095076354.256</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>70004.454</t>
+          <t>96240647817.1554</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>73155.179</t>
+          <t>103605190412.053</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>58681.357</t>
+          <t>78791985878.6134</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>55790.388</t>
+          <t>74356607765.0156</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>63920.927</t>
+          <t>86593955421.3666</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>77231.965</t>
+          <t>108330179728.256</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>69995.091</t>
+          <t>93692377177.038</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>68226.536</t>
+          <t>91974671362.4873</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>62050.26</t>
+          <t>83557434131.7984</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>68979.18</t>
+          <t>92271707714.479</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>67554.62</t>
+          <t>90369731467.4027</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>64585.181</t>
+          <t>86320140186.7713</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>52535.303</t>
+          <t>69336303881.4862</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>58878.622</t>
+          <t>79252073984.1715</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>58722.096</t>
+          <t>79457522355.0403</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>73633.534</t>
+          <t>113820309189.769</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>39913.154</t>
+          <t>56785419472.7672</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>41080.063</t>
+          <t>58002814768.9874</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>39089.878</t>
+          <t>54871514644.1647</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>41332.001</t>
+          <t>59353047054.8122</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>43572.087</t>
+          <t>62807303550.0848</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>41949.395</t>
+          <t>60466061783.9998</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>43370.47</t>
+          <t>64166359117.8152</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>41816.059</t>
+          <t>61546494747.6589</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>52541.498</t>
+          <t>78016552987.48</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>54255.66</t>
+          <t>81277621750.2007</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>55349.708</t>
+          <t>80679127276.2815</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>47632.066</t>
+          <t>67709214426.7406</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>50041.972</t>
+          <t>72970316111.3609</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>47338.981</t>
+          <t>70099973209.8886</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>52274.411</t>
+          <t>76471867407.086</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>54381.461</t>
+          <t>84806059587.8652</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>56287.852</t>
+          <t>83356628327.5616</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>60998.437</t>
+          <t>90698620760.0861</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>66107.072</t>
+          <t>98954480260.4958</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>64164.027</t>
+          <t>100695587376.413</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>93402.686</t>
+          <t>155960983779.169</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>66331.285</t>
+          <t>99946114890.0797</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>66644.816</t>
+          <t>104781714514.386</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>62573.573</t>
+          <t>96659555293.0612</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>67650.907</t>
+          <t>105651330489.354</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>82946.891</t>
+          <t>132840912291.614</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>414846.542</t>
+          <t>424942990687.171</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>205754.21</t>
+          <t>212791095821.376</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>228491.465</t>
+          <t>236343590022.013</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>206317.113</t>
+          <t>214924461564.583</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>245210.382</t>
+          <t>256219384141.196</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>254135.827</t>
+          <t>267407908702.516</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>249808.279</t>
+          <t>262866268696.08</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>251271.671</t>
+          <t>264920604637.927</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>243110.482</t>
+          <t>254303074746.731</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>227038.177</t>
+          <t>240425339104.371</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>269019.866</t>
+          <t>282994004206.942</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>237153.994</t>
+          <t>251783070629.659</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>240904.14</t>
+          <t>249893439027.552</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>260723.562</t>
+          <t>274046490090.858</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>222090.788</t>
+          <t>231788526981.805</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>221878.784</t>
+          <t>233085952039.338</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>230166.078</t>
+          <t>243082461820.688</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>199616.021</t>
+          <t>213025671590.004</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>234527.071</t>
+          <t>246858614672.954</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>198466.384</t>
+          <t>206659978979.994</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>213381.545</t>
+          <t>223013962856.002</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>248823.763</t>
+          <t>258789316820.049</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>254723.405</t>
+          <t>265158794685.839</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>256542.567</t>
+          <t>266386253527.737</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>259096.163</t>
+          <t>268493466205.877</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>278607.041</t>
+          <t>289986982592.919</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>283661.592</t>
+          <t>296080201275.607</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>13371315.302</t>
+          <t>14580490333687.3</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7048597.791</t>
+          <t>7528535139649.73</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7213604.041</t>
+          <t>7765442412425.85</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>6983308.039</t>
+          <t>7594667062322.59</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>7246429.582</t>
+          <t>7913259608642.71</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>7362871.449</t>
+          <t>8077057200130.58</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>7513822.627</t>
+          <t>8238449907915.58</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>7586732.398</t>
+          <t>8316580970540.14</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>7733109.323</t>
+          <t>8461906784812.99</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>8152864.014</t>
+          <t>8929574204109.28</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>8388495.251</t>
+          <t>9164721088433.29</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>8499204.214</t>
+          <t>9297294932392.37</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>8580476.522</t>
+          <t>9335300930547.86</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>8752068.03</t>
+          <t>9606875951564.09</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>8564257.246</t>
+          <t>9376417874810.78</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>8720151.215</t>
+          <t>9551482957694.52</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>9004245.147</t>
+          <t>9884202800823.79</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>9012906.613</t>
+          <t>9909469035212.8</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>9212239.792</t>
+          <t>10082223252975.4</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>9216113.71</t>
+          <t>10022552679791.3</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>9342523.661</t>
+          <t>10090980019682.5</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>10410264.821</t>
+          <t>11201623910197.5</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>10379847.159</t>
+          <t>11079240120318.1</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>10973562.471</t>
+          <t>11723937928643.6</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>11096733.118</t>
+          <t>11785433690304.9</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>12014640.696</t>
+          <t>12785995754338.5</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>12602599.047</t>
+          <t>13412376849767.6</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>3602.459</t>
+          <t>6906964752.3979</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>3583.269</t>
+          <t>6658619899.3585</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>3919.182</t>
+          <t>7218379559.08998</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>4005.595</t>
+          <t>7418234440.06785</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>3819.02</t>
+          <t>6924451401.44217</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>3582.574</t>
+          <t>6443132669.1144</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>3738.6</t>
+          <t>6668515971.60236</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>3644.827</t>
+          <t>6359007108.81624</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>3603.566</t>
+          <t>6428507610.00415</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>3888.546</t>
+          <t>6946556140.92706</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>3969.725</t>
+          <t>7127478737.63477</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>4130.557</t>
+          <t>7521299932.01898</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>3899.878</t>
+          <t>7078536440.02292</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>4096.735</t>
+          <t>7406337146.5082</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>3851.749</t>
+          <t>7075777830.42661</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>3800.167</t>
+          <t>6884928924.41991</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>3701.164</t>
+          <t>6691763417.311</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>3462.522</t>
+          <t>6217607700.72785</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>3278.995</t>
+          <t>5885604989.18536</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>3080.405</t>
+          <t>5553697344.83765</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>2961.008</t>
+          <t>5236775199.74179</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>2994.651</t>
+          <t>5380798121.13387</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>3302.737</t>
+          <t>6242065375.85531</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>3558.938</t>
+          <t>8161803922.91668</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>3564.317</t>
+          <t>6747540049.07491</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>3704.886</t>
+          <t>7000469918.89596</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>3393.383</t>
+          <t>6401659917.53015</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>17317.823</t>
+          <t>26437501123.645</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>10603.718</t>
+          <t>15352748294.3924</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>10173.75</t>
+          <t>14825633052.2401</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>11181.603</t>
+          <t>16267979280.1487</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>10965.694</t>
+          <t>15951085973.3506</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>10578.832</t>
+          <t>15541376762.8747</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>10544.83</t>
+          <t>15518641957.2214</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>10879.516</t>
+          <t>15994739735.2648</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>10527.073</t>
+          <t>15481832578.7578</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>12710.091</t>
+          <t>18726274042.1993</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>12411.637</t>
+          <t>18588099730.3291</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>12727.575</t>
+          <t>19033345993.565</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>10930.606</t>
+          <t>16108708918.1553</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>14155.797</t>
+          <t>20999288107.7856</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>13090.193</t>
+          <t>19699698771.0882</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>12325.225</t>
+          <t>18144984698.4152</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>13285.079</t>
+          <t>20299537494.525</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>13955.699</t>
+          <t>20857424278.8792</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>14995.535</t>
+          <t>22214367312.1522</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>12806.273</t>
+          <t>18972411346.5173</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>12814.197</t>
+          <t>19215639856.5063</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>13624.466</t>
+          <t>20365124236.219</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>12520.719</t>
+          <t>18355943773.2275</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13217.529</t>
+          <t>19864413950.8574</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>11962.072</t>
+          <t>17867610822.1893</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13952.576</t>
+          <t>21029462162.4732</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>16046.454</t>
+          <t>25392349348.9408</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>5675.147</t>
+          <t>7350431757.64257</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>4759.519</t>
+          <t>6199257768.77376</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4839.499</t>
+          <t>6241922762.26904</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5084.102</t>
+          <t>6576738577.03164</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>5523.746</t>
+          <t>7196795769.50214</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>5120.298</t>
+          <t>6606726649.56616</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>4964.079</t>
+          <t>6455436357.03821</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>5345.516</t>
+          <t>6986613545.69893</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>5961.548</t>
+          <t>7792898281.2774</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>5085.565</t>
+          <t>6647024669.35339</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>5249.188</t>
+          <t>6868021747.67897</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>5446.672</t>
+          <t>7144611612.34149</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>5588.321</t>
+          <t>7309627627.41682</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>6897.264</t>
+          <t>9109387916.90491</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>5900.704</t>
+          <t>7776005613.35401</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>6102.933</t>
+          <t>8051573841.55644</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>6429.304</t>
+          <t>8560718587.05565</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>7098.402</t>
+          <t>9536486624.31259</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>7943.979</t>
+          <t>10759759912.3215</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>7010.115</t>
+          <t>9458273326.44399</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>6239.762</t>
+          <t>8292489977.76154</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>5683.949</t>
+          <t>7553119512.44632</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>5506.293</t>
+          <t>7283778437.83299</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>5333.175</t>
+          <t>7049140479.31068</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>5396.04</t>
+          <t>7153471398.76235</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>5574.723</t>
+          <t>7455241867.42887</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>5585.291</t>
+          <t>7474234252.71612</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>26975.427</t>
+          <t>34028975454.2669</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>29662.024</t>
+          <t>36475995387.4522</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>29561.591</t>
+          <t>36499534010.9391</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>30713.1</t>
+          <t>38469788761.8986</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>28285.844</t>
+          <t>35394155260.0943</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>29679.038</t>
+          <t>37506323682.5178</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25458.704</t>
+          <t>32263092659.7961</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>25126.719</t>
+          <t>32376475685.514</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>26134.65</t>
+          <t>33324602504.3889</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>26545.02</t>
+          <t>34123893824.8471</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>26117.113</t>
+          <t>33517783094.4828</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>25788.819</t>
+          <t>33143167367.8312</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>24716.476</t>
+          <t>31193282729.175</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>27166.542</t>
+          <t>34546531923.429</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>25873.804</t>
+          <t>32950032006.6999</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>25068.454</t>
+          <t>31972109845.085</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>25199.907</t>
+          <t>32207089654.5208</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>26702.231</t>
+          <t>34130987094.6464</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>26663.463</t>
+          <t>33996127008.9787</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>22503.311</t>
+          <t>28537046646.7257</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>21000.491</t>
+          <t>26472626252.5599</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>21977.135</t>
+          <t>27610876441.1397</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>24497.328</t>
+          <t>31032136895.0378</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>24240</t>
+          <t>30469987489.1509</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>24945.516</t>
+          <t>31352539601.1584</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>25757.398</t>
+          <t>32583653771.0846</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>24544.583</t>
+          <t>31007220733.585</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1848723.781</t>
+          <t>2354761014128.62</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>667571.981</t>
+          <t>838761886992.354</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>707555.534</t>
+          <t>890920086319.177</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>739669.369</t>
+          <t>929497982196.844</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>820754.493</t>
+          <t>1031792046175.92</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>848434.612</t>
+          <t>1072246293726.69</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>863016.763</t>
+          <t>1089344472943.15</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>907757.857</t>
+          <t>1143189575653.93</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>944793.164</t>
+          <t>1192937719717.06</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>998276.251</t>
+          <t>1255609442968.71</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>1037200.164</t>
+          <t>1301553439064.64</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>1057480.533</t>
+          <t>1327724849986.55</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>1079512.236</t>
+          <t>1356731411765.55</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>1156377.326</t>
+          <t>1449372926636.6</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>1153070.716</t>
+          <t>1448186807354.41</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1195113.165</t>
+          <t>1495601378766.61</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1200024.18</t>
+          <t>1498785359719.06</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>1231472.241</t>
+          <t>1544295032290.17</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>1216545.46</t>
+          <t>1523412265468.18</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>1283125.256</t>
+          <t>1621574962307.54</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>1269975.987</t>
+          <t>1615190075271.75</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>1358827.972</t>
+          <t>1719904919862.57</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>1344146.085</t>
+          <t>1699927172733.66</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>1369086.882</t>
+          <t>1733344687316.83</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>1340935.383</t>
+          <t>1689163329642.39</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>1448419.939</t>
+          <t>1825069465941.82</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>1525925.319</t>
+          <t>1932510433326.3</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>270257.73</t>
+          <t>342641364787.828</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>201291.585</t>
+          <t>251123323710.678</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>209379.826</t>
+          <t>261999151328.66</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>218380.146</t>
+          <t>274694259986.004</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>216200.694</t>
+          <t>272138797859.998</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>219326.745</t>
+          <t>277017748837.04</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>223383.247</t>
+          <t>281977996112.129</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>226871.154</t>
+          <t>287070857067.899</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>235054.06</t>
+          <t>296599518744.874</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>240335.961</t>
+          <t>303087808576.703</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>237014.239</t>
+          <t>298057837109.172</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>241897.922</t>
+          <t>303669656306.485</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>246474.882</t>
+          <t>309600652976.655</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>274042.595</t>
+          <t>345924211031.831</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>283981.531</t>
+          <t>358439234839.86</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>286445.77</t>
+          <t>358849704004.781</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>303414.704</t>
+          <t>380492415967.491</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>307758.096</t>
+          <t>387945904504.254</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>304519.656</t>
+          <t>382104741881.935</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>281527.038</t>
+          <t>352080856798.333</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>273251.554</t>
+          <t>341039867614.89</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>302769.376</t>
+          <t>378628981541.783</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>281742.734</t>
+          <t>352382251544.368</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>283334.297</t>
+          <t>354047285810.551</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>254893.742</t>
+          <t>318832074143.995</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>252371.605</t>
+          <t>316170888188.848</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>244525.493</t>
+          <t>306943286314.084</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>636727.07</t>
+          <t>860418689445.036</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>431633.969</t>
+          <t>571979256733.95</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>428029.173</t>
+          <t>567979422136.642</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>426666.609</t>
+          <t>559769455228.06</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>430073.596</t>
+          <t>562263815402.385</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>418575.081</t>
+          <t>547884888804.595</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>393353.772</t>
+          <t>515722610207.345</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>391597.916</t>
+          <t>504707883193.175</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>420734.305</t>
+          <t>542454166613.031</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>421003.473</t>
+          <t>548361854462.972</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>409765.692</t>
+          <t>531753709695.97</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>417698.691</t>
+          <t>538501637125.594</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>436346.587</t>
+          <t>565837980189.135</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>406656.23</t>
+          <t>525348194512.716</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>396651.268</t>
+          <t>510687323553.601</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>434844.094</t>
+          <t>558350171580.815</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>399854.078</t>
+          <t>513167835210.138</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>396447.568</t>
+          <t>508149866282.197</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>394541.306</t>
+          <t>504833247009.381</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>408867.327</t>
+          <t>525537600057.897</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>353286.801</t>
+          <t>453971558275.509</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>335526.393</t>
+          <t>432430555771.691</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>323064.201</t>
+          <t>412676020955.875</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>366074.55</t>
+          <t>469204306404.065</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>395002.399</t>
+          <t>507189279928.433</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>438360.696</t>
+          <t>562860294937.645</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>437739.053</t>
+          <t>557636829198.3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>1301752.823</t>
+          <t>1566238051229.28</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>669050.275</t>
+          <t>821380972685.256</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>682985.491</t>
+          <t>839268220991.6</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>722279.143</t>
+          <t>891181976290.274</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>738776.479</t>
+          <t>911759996421.256</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>763986.675</t>
+          <t>941680797850.345</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>775405.972</t>
+          <t>958371940619.132</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>783257.817</t>
+          <t>964888672039.162</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>809914.369</t>
+          <t>994959420948.995</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>830461.225</t>
+          <t>1021364323604.48</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>849370.643</t>
+          <t>1042620425002.8</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>870032.33</t>
+          <t>1070464945528.8</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>889988.317</t>
+          <t>1089330329973.09</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>945488.237</t>
+          <t>1165519350363.93</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>940091.065</t>
+          <t>1151833977170.25</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>966211.574</t>
+          <t>1188218726344.34</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1032404.777</t>
+          <t>1276838564478.34</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>1028223.58</t>
+          <t>1268505401918.89</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>1037495.925</t>
+          <t>1271841223602.18</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>989921.321</t>
+          <t>1192718351637.57</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>986942.214</t>
+          <t>1185365992674.1</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>1083330.059</t>
+          <t>1303602797956.62</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>1011649.571</t>
+          <t>1215200249304.72</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>1027140.155</t>
+          <t>1229490168573.38</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>1060091.132</t>
+          <t>1275091140919.13</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>1164840.451</t>
+          <t>1401376364775.38</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>1193489.751</t>
+          <t>1436336071136.01</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>133992.804</t>
+          <t>160385751924.862</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>54046.609</t>
+          <t>64093997543.0552</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>58890.544</t>
+          <t>70871892580.5334</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61310.881</t>
+          <t>73761578826.0267</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>64008.595</t>
+          <t>78477248281.556</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>70615.696</t>
+          <t>87038886967.4174</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>77758.025</t>
+          <t>97204349652.363</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>85367.805</t>
+          <t>105290428302.277</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>82625.922</t>
+          <t>100812445903.663</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>96330.056</t>
+          <t>118423010897.911</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>101655.09</t>
+          <t>124385495058.347</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>110703.37</t>
+          <t>135876964224.222</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>120494.884</t>
+          <t>145944223222.989</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>142146.868</t>
+          <t>174289034553.502</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>137543.405</t>
+          <t>168728605042.787</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>141049.985</t>
+          <t>172484830126.364</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>147507.943</t>
+          <t>181319709966.183</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>157465.824</t>
+          <t>194079804102.094</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>159755.098</t>
+          <t>195531466886.947</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>147314.349</t>
+          <t>180036790283.691</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>138623.74</t>
+          <t>168994120867.219</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>140161.697</t>
+          <t>171030626821.473</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>141269.29</t>
+          <t>171510551148.541</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>142335.19</t>
+          <t>172954292794.93</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>138147.787</t>
+          <t>167158795527.744</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>156871</t>
+          <t>190882422278.749</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>158601.141</t>
+          <t>192812872948.639</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>gross_output.s.mv</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
